--- a/Defect_Tracker_Template_v0_1.xlsx
+++ b/Defect_Tracker_Template_v0_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -925,6 +925,226 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Security Dev</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Excessive nesting depth false positive (counted 5 levels of nesting on Java try-with-resources with while loop).</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Backend Dev</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>False Positive</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Refactored compute_nesting_depth in java_analyzer.py to identify and ignore try-with-resources declarations from nesting depth counter.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Proper try-with-resources code passes with 0 false positive nesting warnings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Frontend Dev</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Scan history displayed truncated 2-line snippets without expanding full code and finding remediation details.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Frontend Dev</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>UI / UX</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Redesigned Scan History page into full Audit Dashboard with detail retrieval (/scan/{id}), source code viewer, metric cards, and filters.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Users can inspect full code, view all findings, copy code, and reload into editor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Security Dev</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Java remediation suggested manual resource management (connection.close()) instead of modern try-with-resources.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AI Eng</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Remediation Logic</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Enforced try-with-resources in Java remediation prompts and secure fix generators for auto-closable JDBC connections.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Remediated code complies with modern Java SE best practices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Backend Dev</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Scan history delete operation failed to cascade-delete foreign key child records (ChatSession, TokenUsage, FixHistory).</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Backend Dev</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Database / Integrity</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Implemented cascading foreign key cleanup in DELETE /api/v1/submit/{scan_id} across all related tables.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Database integrity preserved with clean zero-orphan deletion.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
